--- a/Acompanhamento_Sessoes_Nexus.xlsx
+++ b/Acompanhamento_Sessoes_Nexus.xlsx
@@ -75941,13 +75941,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCBDFF85-1EAD-4E71-9192-CDA29B8F46DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BEB73E9-DB10-4F62-9A3F-79345D00B1F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7FBB82-FBA5-4CA3-98E2-60168A91C766}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FBA3112-CC3D-4134-91B6-667340991958}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF8B5AE9-FE09-4C41-9162-F0BE79D38FD7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD18226-1DDE-4603-B041-C1804C96E792}"/>
 </file>